--- a/AI Planning/Job Scheduling/Flow Shop/problemset/solution/neh/restaurante-10j-3m-5_60tr-same_per_jobd_neh.xlsx
+++ b/AI Planning/Job Scheduling/Flow Shop/problemset/solution/neh/restaurante-10j-3m-5_60tr-same_per_jobd_neh.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,28 +458,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cliente 6</t>
+          <t>Cliente 7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Postre</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cliente 6</t>
+          <t>Cliente 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cliente 6</t>
+          <t>Cliente 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -509,103 +509,103 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cliente 9</t>
+          <t>Cliente 3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Plato fuerte</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cliente 9</t>
+          <t>Cliente 4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Plato fuerte</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cliente 9</t>
+          <t>Cliente 5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Postre</t>
+          <t>Plato fuerte</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cliente 2</t>
+          <t>Cliente 5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Postre</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cliente 2</t>
+          <t>Cliente 0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -614,475 +614,160 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cliente 2</t>
+          <t>Cliente 8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Postre</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>15</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cliente 7</t>
+          <t>Cliente 8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Postre</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cliente 7</t>
+          <t>Cliente 6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Plato fuerte</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cliente 7</t>
+          <t>Cliente 6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Postre</t>
+          <t>Plato fuerte</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>54</v>
+        <v>140</v>
       </c>
       <c r="E13" t="n">
-        <v>54</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cliente 0</t>
+          <t>Cliente 6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Entrada</t>
+          <t>Postre</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cliente 0</t>
+          <t>Cliente 9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Plato fuerte</t>
+          <t>Entrada</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="E15" t="n">
-        <v>54</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cliente 0</t>
+          <t>Cliente 9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Postre</t>
+          <t>Plato fuerte</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>54</v>
+        <v>194</v>
       </c>
       <c r="E16" t="n">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Cliente 8</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Cliente 8</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Plato fuerte</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>24</v>
-      </c>
-      <c r="D18" t="n">
-        <v>54</v>
-      </c>
-      <c r="E18" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Cliente 8</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Postre</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>24</v>
-      </c>
-      <c r="D19" t="n">
-        <v>99</v>
-      </c>
-      <c r="E19" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Cliente 3</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>22</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Cliente 3</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Plato fuerte</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>22</v>
-      </c>
-      <c r="D21" t="n">
-        <v>78</v>
-      </c>
-      <c r="E21" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Cliente 3</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Postre</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>22</v>
-      </c>
-      <c r="D22" t="n">
-        <v>123</v>
-      </c>
-      <c r="E22" t="n">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Cliente 1</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>26</v>
-      </c>
-      <c r="D23" t="n">
-        <v>22</v>
-      </c>
-      <c r="E23" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Cliente 1</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Plato fuerte</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>26</v>
-      </c>
-      <c r="D24" t="n">
-        <v>100</v>
-      </c>
-      <c r="E24" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Cliente 1</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Postre</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>26</v>
-      </c>
-      <c r="D25" t="n">
-        <v>145</v>
-      </c>
-      <c r="E25" t="n">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Cliente 4</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>46</v>
-      </c>
-      <c r="D26" t="n">
-        <v>48</v>
-      </c>
-      <c r="E26" t="n">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Cliente 4</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Plato fuerte</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>46</v>
-      </c>
-      <c r="D27" t="n">
-        <v>126</v>
-      </c>
-      <c r="E27" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Cliente 4</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Postre</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>172</v>
-      </c>
-      <c r="E28" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Cliente 5</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>24</v>
-      </c>
-      <c r="D29" t="n">
-        <v>94</v>
-      </c>
-      <c r="E29" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Cliente 5</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Plato fuerte</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>172</v>
-      </c>
-      <c r="E30" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Cliente 5</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Postre</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>172</v>
-      </c>
-      <c r="E31" t="n">
-        <v>172</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
